--- a/data/zone_import/mining/矿业专区_找图清单.xlsx
+++ b/data/zone_import/mining/矿业专区_找图清单.xlsx
@@ -11,7 +11,7 @@
     <sheet name="交付要求" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'商品清单'!$A$1:$I$765</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'商品清单'!$A$1:$I$764</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I765"/>
+  <dimension ref="A1:I764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30012,12 +30012,12 @@
       </c>
       <c r="B660" s="2" t="inlineStr">
         <is>
-          <t>MG-P7CEF0C8E8445</t>
+          <t>MG-P5FD87C0A2144</t>
         </is>
       </c>
       <c r="C660" s="2" t="inlineStr">
         <is>
-          <t>班报表</t>
+          <t>锯片</t>
         </is>
       </c>
       <c r="D660" s="2" t="inlineStr">
@@ -30029,7 +30029,7 @@
       <c r="F660" s="2" t="inlineStr"/>
       <c r="G660" s="2" t="inlineStr">
         <is>
-          <t>本</t>
+          <t>个</t>
         </is>
       </c>
       <c r="H660" s="2" t="inlineStr">
@@ -30039,7 +30039,7 @@
       </c>
       <c r="I660" s="2" t="inlineStr">
         <is>
-          <t>600:新R014</t>
+          <t>600:新R015</t>
         </is>
       </c>
     </row>
@@ -30049,24 +30049,24 @@
       </c>
       <c r="B661" s="2" t="inlineStr">
         <is>
-          <t>MG-P5FD87C0A2144</t>
+          <t>MG-P93DAE9AB512E</t>
         </is>
       </c>
       <c r="C661" s="2" t="inlineStr">
         <is>
-          <t>锯片</t>
+          <t>黄油</t>
         </is>
       </c>
       <c r="D661" s="2" t="inlineStr">
         <is>
-          <t>未列</t>
+          <t>毛毛虫黄油30支/箱；单支净重待核</t>
         </is>
       </c>
       <c r="E661" s="2" t="inlineStr"/>
       <c r="F661" s="2" t="inlineStr"/>
       <c r="G661" s="2" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="H661" s="2" t="inlineStr">
@@ -30076,7 +30076,7 @@
       </c>
       <c r="I661" s="2" t="inlineStr">
         <is>
-          <t>600:新R015</t>
+          <t>600:新R017</t>
         </is>
       </c>
     </row>
@@ -30086,24 +30086,24 @@
       </c>
       <c r="B662" s="2" t="inlineStr">
         <is>
-          <t>MG-P93DAE9AB512E</t>
+          <t>MG-PBF4ED16D7665</t>
         </is>
       </c>
       <c r="C662" s="2" t="inlineStr">
         <is>
-          <t>黄油</t>
+          <t>聚丙烯酰胺好</t>
         </is>
       </c>
       <c r="D662" s="2" t="inlineStr">
         <is>
-          <t>毛毛虫黄油30支/箱；单支净重待核</t>
+          <t>3000万</t>
         </is>
       </c>
       <c r="E662" s="2" t="inlineStr"/>
       <c r="F662" s="2" t="inlineStr"/>
       <c r="G662" s="2" t="inlineStr">
         <is>
-          <t>箱</t>
+          <t>吨</t>
         </is>
       </c>
       <c r="H662" s="2" t="inlineStr">
@@ -30113,7 +30113,7 @@
       </c>
       <c r="I662" s="2" t="inlineStr">
         <is>
-          <t>600:新R017</t>
+          <t>600:新R022</t>
         </is>
       </c>
     </row>
@@ -30123,17 +30123,17 @@
       </c>
       <c r="B663" s="2" t="inlineStr">
         <is>
-          <t>MG-PBF4ED16D7665</t>
+          <t>MG-P63A5AFE327CD</t>
         </is>
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>聚丙烯酰胺好</t>
+          <t>腐殖酸钾</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
         <is>
-          <t>3000万</t>
+          <t>未列</t>
         </is>
       </c>
       <c r="E663" s="2" t="inlineStr"/>
@@ -30150,7 +30150,7 @@
       </c>
       <c r="I663" s="2" t="inlineStr">
         <is>
-          <t>600:新R022</t>
+          <t>600:新R023</t>
         </is>
       </c>
     </row>
@@ -30160,12 +30160,12 @@
       </c>
       <c r="B664" s="2" t="inlineStr">
         <is>
-          <t>MG-P63A5AFE327CD</t>
+          <t>MG-P8D78F0C01047</t>
         </is>
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>腐殖酸钾</t>
+          <t>防塌剂</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
@@ -30187,7 +30187,7 @@
       </c>
       <c r="I664" s="2" t="inlineStr">
         <is>
-          <t>600:新R023</t>
+          <t>600:新R024</t>
         </is>
       </c>
     </row>
@@ -30197,24 +30197,24 @@
       </c>
       <c r="B665" s="2" t="inlineStr">
         <is>
-          <t>MG-P8D78F0C01047</t>
+          <t>MG-PB1271EB76F2B</t>
         </is>
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>防塌剂</t>
+          <t>阀座</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
         <is>
-          <t>未列</t>
+          <t>大象150</t>
         </is>
       </c>
       <c r="E665" s="2" t="inlineStr"/>
       <c r="F665" s="2" t="inlineStr"/>
       <c r="G665" s="2" t="inlineStr">
         <is>
-          <t>吨</t>
+          <t>个</t>
         </is>
       </c>
       <c r="H665" s="2" t="inlineStr">
@@ -30224,7 +30224,7 @@
       </c>
       <c r="I665" s="2" t="inlineStr">
         <is>
-          <t>600:新R024</t>
+          <t>600:新R026</t>
         </is>
       </c>
     </row>
@@ -30234,12 +30234,12 @@
       </c>
       <c r="B666" s="2" t="inlineStr">
         <is>
-          <t>MG-PB1271EB76F2B</t>
+          <t>MG-PE51C2B9E3DF3</t>
         </is>
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>阀座</t>
+          <t>钢球</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
@@ -30251,7 +30251,7 @@
       <c r="F666" s="2" t="inlineStr"/>
       <c r="G666" s="2" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>只</t>
         </is>
       </c>
       <c r="H666" s="2" t="inlineStr">
@@ -30261,7 +30261,7 @@
       </c>
       <c r="I666" s="2" t="inlineStr">
         <is>
-          <t>600:新R026</t>
+          <t>600:新R027、600:新R076、600:新R115</t>
         </is>
       </c>
     </row>
@@ -30271,12 +30271,12 @@
       </c>
       <c r="B667" s="2" t="inlineStr">
         <is>
-          <t>MG-PE51C2B9E3DF3</t>
+          <t>MG-PF77059583DBA</t>
         </is>
       </c>
       <c r="C667" s="2" t="inlineStr">
         <is>
-          <t>钢球</t>
+          <t>拉杆</t>
         </is>
       </c>
       <c r="D667" s="2" t="inlineStr">
@@ -30288,7 +30288,7 @@
       <c r="F667" s="2" t="inlineStr"/>
       <c r="G667" s="2" t="inlineStr">
         <is>
-          <t>只</t>
+          <t>个</t>
         </is>
       </c>
       <c r="H667" s="2" t="inlineStr">
@@ -30298,7 +30298,7 @@
       </c>
       <c r="I667" s="2" t="inlineStr">
         <is>
-          <t>600:新R027、600:新R076、600:新R115</t>
+          <t>600:新R028</t>
         </is>
       </c>
     </row>
@@ -30308,12 +30308,12 @@
       </c>
       <c r="B668" s="2" t="inlineStr">
         <is>
-          <t>MG-PF77059583DBA</t>
+          <t>MG-P4110A668E936</t>
         </is>
       </c>
       <c r="C668" s="2" t="inlineStr">
         <is>
-          <t>拉杆</t>
+          <t>泥浆泵压力表</t>
         </is>
       </c>
       <c r="D668" s="2" t="inlineStr">
@@ -30335,7 +30335,7 @@
       </c>
       <c r="I668" s="2" t="inlineStr">
         <is>
-          <t>600:新R028</t>
+          <t>600:新R029</t>
         </is>
       </c>
     </row>
@@ -30345,24 +30345,24 @@
       </c>
       <c r="B669" s="2" t="inlineStr">
         <is>
-          <t>MG-P4110A668E936</t>
+          <t>MG-P53AE2E443F78</t>
         </is>
       </c>
       <c r="C669" s="2" t="inlineStr">
         <is>
-          <t>泥浆泵压力表</t>
+          <t>泥浆泵吸水管</t>
         </is>
       </c>
       <c r="D669" s="2" t="inlineStr">
         <is>
-          <t>大象150</t>
+          <t>管径50（单位待核）；按米计价</t>
         </is>
       </c>
       <c r="E669" s="2" t="inlineStr"/>
       <c r="F669" s="2" t="inlineStr"/>
       <c r="G669" s="2" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>米</t>
         </is>
       </c>
       <c r="H669" s="2" t="inlineStr">
@@ -30372,7 +30372,7 @@
       </c>
       <c r="I669" s="2" t="inlineStr">
         <is>
-          <t>600:新R029</t>
+          <t>600:新R030</t>
         </is>
       </c>
     </row>
@@ -30382,24 +30382,24 @@
       </c>
       <c r="B670" s="2" t="inlineStr">
         <is>
-          <t>MG-P53AE2E443F78</t>
+          <t>MG-P76852EF775DA</t>
         </is>
       </c>
       <c r="C670" s="2" t="inlineStr">
         <is>
-          <t>泥浆泵吸水管</t>
+          <t>水接头水封</t>
         </is>
       </c>
       <c r="D670" s="2" t="inlineStr">
         <is>
-          <t>管径50（单位待核）；按米计价</t>
+          <t>未列</t>
         </is>
       </c>
       <c r="E670" s="2" t="inlineStr"/>
       <c r="F670" s="2" t="inlineStr"/>
       <c r="G670" s="2" t="inlineStr">
         <is>
-          <t>米</t>
+          <t>组</t>
         </is>
       </c>
       <c r="H670" s="2" t="inlineStr">
@@ -30409,7 +30409,7 @@
       </c>
       <c r="I670" s="2" t="inlineStr">
         <is>
-          <t>600:新R030</t>
+          <t>600:新R031</t>
         </is>
       </c>
     </row>
@@ -30419,12 +30419,12 @@
       </c>
       <c r="B671" s="2" t="inlineStr">
         <is>
-          <t>MG-P76852EF775DA</t>
+          <t>MG-P7502559D1E96</t>
         </is>
       </c>
       <c r="C671" s="2" t="inlineStr">
         <is>
-          <t>水接头水封</t>
+          <t>水芯管</t>
         </is>
       </c>
       <c r="D671" s="2" t="inlineStr">
@@ -30436,7 +30436,7 @@
       <c r="F671" s="2" t="inlineStr"/>
       <c r="G671" s="2" t="inlineStr">
         <is>
-          <t>组</t>
+          <t>个</t>
         </is>
       </c>
       <c r="H671" s="2" t="inlineStr">
@@ -30446,7 +30446,7 @@
       </c>
       <c r="I671" s="2" t="inlineStr">
         <is>
-          <t>600:新R031</t>
+          <t>600:新R032</t>
         </is>
       </c>
     </row>
@@ -30456,17 +30456,17 @@
       </c>
       <c r="B672" s="2" t="inlineStr">
         <is>
-          <t>MG-P7502559D1E96</t>
+          <t>MG-PB29414772FFD</t>
         </is>
       </c>
       <c r="C672" s="2" t="inlineStr">
         <is>
-          <t>水芯管</t>
+          <t>水接头总成</t>
         </is>
       </c>
       <c r="D672" s="2" t="inlineStr">
         <is>
-          <t>未列</t>
+          <t>中晟</t>
         </is>
       </c>
       <c r="E672" s="2" t="inlineStr"/>
@@ -30483,7 +30483,7 @@
       </c>
       <c r="I672" s="2" t="inlineStr">
         <is>
-          <t>600:新R032</t>
+          <t>600:新R033</t>
         </is>
       </c>
     </row>
@@ -30493,17 +30493,17 @@
       </c>
       <c r="B673" s="2" t="inlineStr">
         <is>
-          <t>MG-PB29414772FFD</t>
+          <t>MG-PF427D1FAD78B</t>
         </is>
       </c>
       <c r="C673" s="2" t="inlineStr">
         <is>
-          <t>水接头总成</t>
+          <t>水接头轴承</t>
         </is>
       </c>
       <c r="D673" s="2" t="inlineStr">
         <is>
-          <t>中晟</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="E673" s="2" t="inlineStr"/>
@@ -30520,7 +30520,7 @@
       </c>
       <c r="I673" s="2" t="inlineStr">
         <is>
-          <t>600:新R033</t>
+          <t>600:新R034</t>
         </is>
       </c>
     </row>
@@ -30530,17 +30530,17 @@
       </c>
       <c r="B674" s="2" t="inlineStr">
         <is>
-          <t>MG-PF427D1FAD78B</t>
+          <t>MG-P66ACD581AE7F</t>
         </is>
       </c>
       <c r="C674" s="2" t="inlineStr">
         <is>
-          <t>水接头轴承</t>
+          <t>水接头骨架油封</t>
         </is>
       </c>
       <c r="D674" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>30/40/8</t>
         </is>
       </c>
       <c r="E674" s="2" t="inlineStr"/>
@@ -30557,7 +30557,7 @@
       </c>
       <c r="I674" s="2" t="inlineStr">
         <is>
-          <t>600:新R034</t>
+          <t>600:新R035</t>
         </is>
       </c>
     </row>
@@ -30567,17 +30567,17 @@
       </c>
       <c r="B675" s="2" t="inlineStr">
         <is>
-          <t>MG-P66ACD581AE7F</t>
+          <t>MG-PDC48F4E59B63</t>
         </is>
       </c>
       <c r="C675" s="2" t="inlineStr">
         <is>
-          <t>水接头骨架油封</t>
+          <t>轴承</t>
         </is>
       </c>
       <c r="D675" s="2" t="inlineStr">
         <is>
-          <t>30/40/8</t>
+          <t>61919</t>
         </is>
       </c>
       <c r="E675" s="2" t="inlineStr"/>
@@ -30594,7 +30594,7 @@
       </c>
       <c r="I675" s="2" t="inlineStr">
         <is>
-          <t>600:新R035</t>
+          <t>600:新R036、600:新R037、600:新R038</t>
         </is>
       </c>
     </row>
@@ -30604,17 +30604,17 @@
       </c>
       <c r="B676" s="2" t="inlineStr">
         <is>
-          <t>MG-PDC48F4E59B63</t>
+          <t>MG-P34D7FC13FC84</t>
         </is>
       </c>
       <c r="C676" s="2" t="inlineStr">
         <is>
-          <t>轴承</t>
+          <t>油抽子</t>
         </is>
       </c>
       <c r="D676" s="2" t="inlineStr">
         <is>
-          <t>61919</t>
+          <t>电动</t>
         </is>
       </c>
       <c r="E676" s="2" t="inlineStr"/>
@@ -30631,7 +30631,7 @@
       </c>
       <c r="I676" s="2" t="inlineStr">
         <is>
-          <t>600:新R036、600:新R037、600:新R038</t>
+          <t>600:新R039</t>
         </is>
       </c>
     </row>
@@ -30641,24 +30641,24 @@
       </c>
       <c r="B677" s="2" t="inlineStr">
         <is>
-          <t>MG-P34D7FC13FC84</t>
+          <t>MG-P1274FB473140</t>
         </is>
       </c>
       <c r="C677" s="2" t="inlineStr">
         <is>
-          <t>油抽子</t>
+          <t>抽水泵水管</t>
         </is>
       </c>
       <c r="D677" s="2" t="inlineStr">
         <is>
-          <t>电动</t>
+          <t>32#</t>
         </is>
       </c>
       <c r="E677" s="2" t="inlineStr"/>
       <c r="F677" s="2" t="inlineStr"/>
       <c r="G677" s="2" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>米</t>
         </is>
       </c>
       <c r="H677" s="2" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="I677" s="2" t="inlineStr">
         <is>
-          <t>600:新R039</t>
+          <t>600:新R041</t>
         </is>
       </c>
     </row>
@@ -30678,24 +30678,24 @@
       </c>
       <c r="B678" s="2" t="inlineStr">
         <is>
-          <t>MG-P1274FB473140</t>
+          <t>MG-P82077C671CCF</t>
         </is>
       </c>
       <c r="C678" s="2" t="inlineStr">
         <is>
-          <t>抽水泵水管</t>
+          <t>钻杆-1.5m开孔</t>
         </is>
       </c>
       <c r="D678" s="2" t="inlineStr">
         <is>
-          <t>32#</t>
+          <t>HTW</t>
         </is>
       </c>
       <c r="E678" s="2" t="inlineStr"/>
       <c r="F678" s="2" t="inlineStr"/>
       <c r="G678" s="2" t="inlineStr">
         <is>
-          <t>米</t>
+          <t>根</t>
         </is>
       </c>
       <c r="H678" s="2" t="inlineStr">
@@ -30705,7 +30705,7 @@
       </c>
       <c r="I678" s="2" t="inlineStr">
         <is>
-          <t>600:新R041</t>
+          <t>600:新R044</t>
         </is>
       </c>
     </row>
@@ -30715,12 +30715,12 @@
       </c>
       <c r="B679" s="2" t="inlineStr">
         <is>
-          <t>MG-P82077C671CCF</t>
+          <t>MG-P0290E8175DED</t>
         </is>
       </c>
       <c r="C679" s="2" t="inlineStr">
         <is>
-          <t>钻杆-1.5m开孔</t>
+          <t>跟管钻头</t>
         </is>
       </c>
       <c r="D679" s="2" t="inlineStr">
@@ -30732,7 +30732,7 @@
       <c r="F679" s="2" t="inlineStr"/>
       <c r="G679" s="2" t="inlineStr">
         <is>
-          <t>根</t>
+          <t>只</t>
         </is>
       </c>
       <c r="H679" s="2" t="inlineStr">
@@ -30742,7 +30742,7 @@
       </c>
       <c r="I679" s="2" t="inlineStr">
         <is>
-          <t>600:新R044</t>
+          <t>600:新R045</t>
         </is>
       </c>
     </row>
@@ -30752,12 +30752,12 @@
       </c>
       <c r="B680" s="2" t="inlineStr">
         <is>
-          <t>MG-P0290E8175DED</t>
+          <t>MG-P04ECCF316FCE</t>
         </is>
       </c>
       <c r="C680" s="2" t="inlineStr">
         <is>
-          <t>跟管钻头</t>
+          <t>管钳</t>
         </is>
       </c>
       <c r="D680" s="2" t="inlineStr">
@@ -30769,7 +30769,7 @@
       <c r="F680" s="2" t="inlineStr"/>
       <c r="G680" s="2" t="inlineStr">
         <is>
-          <t>只</t>
+          <t>把</t>
         </is>
       </c>
       <c r="H680" s="2" t="inlineStr">
@@ -30779,7 +30779,7 @@
       </c>
       <c r="I680" s="2" t="inlineStr">
         <is>
-          <t>600:新R045</t>
+          <t>600:新R046、600:补R089</t>
         </is>
       </c>
     </row>
@@ -30789,12 +30789,12 @@
       </c>
       <c r="B681" s="2" t="inlineStr">
         <is>
-          <t>MG-P04ECCF316FCE</t>
+          <t>MG-P9745B9EAA8A0</t>
         </is>
       </c>
       <c r="C681" s="2" t="inlineStr">
         <is>
-          <t>管钳</t>
+          <t>自由钳</t>
         </is>
       </c>
       <c r="D681" s="2" t="inlineStr">
@@ -30816,7 +30816,7 @@
       </c>
       <c r="I681" s="2" t="inlineStr">
         <is>
-          <t>600:新R046、600:补R089</t>
+          <t>600:新R047</t>
         </is>
       </c>
     </row>
@@ -30826,17 +30826,17 @@
       </c>
       <c r="B682" s="2" t="inlineStr">
         <is>
-          <t>MG-P9745B9EAA8A0</t>
+          <t>MG-P4B72C1BFB8E3</t>
         </is>
       </c>
       <c r="C682" s="2" t="inlineStr">
         <is>
-          <t>自由钳</t>
+          <t>小管钳</t>
         </is>
       </c>
       <c r="D682" s="2" t="inlineStr">
         <is>
-          <t>HTW</t>
+          <t>80D</t>
         </is>
       </c>
       <c r="E682" s="2" t="inlineStr"/>
@@ -30853,7 +30853,7 @@
       </c>
       <c r="I682" s="2" t="inlineStr">
         <is>
-          <t>600:新R047</t>
+          <t>600:新R048</t>
         </is>
       </c>
     </row>
@@ -30863,24 +30863,24 @@
       </c>
       <c r="B683" s="2" t="inlineStr">
         <is>
-          <t>MG-P4B72C1BFB8E3</t>
+          <t>MG-P784450A8F854</t>
         </is>
       </c>
       <c r="C683" s="2" t="inlineStr">
         <is>
-          <t>小管钳</t>
+          <t>钻具头总成</t>
         </is>
       </c>
       <c r="D683" s="2" t="inlineStr">
         <is>
-          <t>80D</t>
+          <t>HTW</t>
         </is>
       </c>
       <c r="E683" s="2" t="inlineStr"/>
       <c r="F683" s="2" t="inlineStr"/>
       <c r="G683" s="2" t="inlineStr">
         <is>
-          <t>把</t>
+          <t>套</t>
         </is>
       </c>
       <c r="H683" s="2" t="inlineStr">
@@ -30890,7 +30890,7 @@
       </c>
       <c r="I683" s="2" t="inlineStr">
         <is>
-          <t>600:新R048</t>
+          <t>600:新R049</t>
         </is>
       </c>
     </row>
@@ -30900,24 +30900,24 @@
       </c>
       <c r="B684" s="2" t="inlineStr">
         <is>
-          <t>MG-P784450A8F854</t>
+          <t>MG-P7AAE0CF55ED9</t>
         </is>
       </c>
       <c r="C684" s="2" t="inlineStr">
         <is>
-          <t>钻具头总成</t>
+          <t>内管</t>
         </is>
       </c>
       <c r="D684" s="2" t="inlineStr">
         <is>
-          <t>HTW</t>
+          <t>HTW-3m</t>
         </is>
       </c>
       <c r="E684" s="2" t="inlineStr"/>
       <c r="F684" s="2" t="inlineStr"/>
       <c r="G684" s="2" t="inlineStr">
         <is>
-          <t>套</t>
+          <t>根</t>
         </is>
       </c>
       <c r="H684" s="2" t="inlineStr">
@@ -30927,7 +30927,7 @@
       </c>
       <c r="I684" s="2" t="inlineStr">
         <is>
-          <t>600:新R049</t>
+          <t>600:新R050、600:新R051、600:新R081</t>
         </is>
       </c>
     </row>
@@ -30937,24 +30937,24 @@
       </c>
       <c r="B685" s="2" t="inlineStr">
         <is>
-          <t>MG-P7AAE0CF55ED9</t>
+          <t>MG-PB9B27E41EF22</t>
         </is>
       </c>
       <c r="C685" s="2" t="inlineStr">
         <is>
-          <t>内管</t>
+          <t>卡簧</t>
         </is>
       </c>
       <c r="D685" s="2" t="inlineStr">
         <is>
-          <t>HTW-3m</t>
+          <t>HTW</t>
         </is>
       </c>
       <c r="E685" s="2" t="inlineStr"/>
       <c r="F685" s="2" t="inlineStr"/>
       <c r="G685" s="2" t="inlineStr">
         <is>
-          <t>根</t>
+          <t>只</t>
         </is>
       </c>
       <c r="H685" s="2" t="inlineStr">
@@ -30964,7 +30964,7 @@
       </c>
       <c r="I685" s="2" t="inlineStr">
         <is>
-          <t>600:新R050、600:新R051、600:新R081</t>
+          <t>600:新R052、600:新R082</t>
         </is>
       </c>
     </row>
@@ -30974,12 +30974,12 @@
       </c>
       <c r="B686" s="2" t="inlineStr">
         <is>
-          <t>MG-PB9B27E41EF22</t>
+          <t>MG-PC2A7F484E573</t>
         </is>
       </c>
       <c r="C686" s="2" t="inlineStr">
         <is>
-          <t>卡簧</t>
+          <t>卡簧座</t>
         </is>
       </c>
       <c r="D686" s="2" t="inlineStr">
@@ -31001,7 +31001,7 @@
       </c>
       <c r="I686" s="2" t="inlineStr">
         <is>
-          <t>600:新R052、600:新R082</t>
+          <t>600:新R053、600:新R083</t>
         </is>
       </c>
     </row>
@@ -31011,12 +31011,12 @@
       </c>
       <c r="B687" s="2" t="inlineStr">
         <is>
-          <t>MG-PC2A7F484E573</t>
+          <t>MG-P0F2790058E23</t>
         </is>
       </c>
       <c r="C687" s="2" t="inlineStr">
         <is>
-          <t>卡簧座</t>
+          <t>弹卡挡头</t>
         </is>
       </c>
       <c r="D687" s="2" t="inlineStr">
@@ -31038,7 +31038,7 @@
       </c>
       <c r="I687" s="2" t="inlineStr">
         <is>
-          <t>600:新R053、600:新R083</t>
+          <t>600:新R054、600:新R084</t>
         </is>
       </c>
     </row>
@@ -31048,12 +31048,12 @@
       </c>
       <c r="B688" s="2" t="inlineStr">
         <is>
-          <t>MG-P0F2790058E23</t>
+          <t>MG-P31074601A840</t>
         </is>
       </c>
       <c r="C688" s="2" t="inlineStr">
         <is>
-          <t>弹卡挡头</t>
+          <t>弹卡室</t>
         </is>
       </c>
       <c r="D688" s="2" t="inlineStr">
@@ -31075,7 +31075,7 @@
       </c>
       <c r="I688" s="2" t="inlineStr">
         <is>
-          <t>600:新R054、600:新R084</t>
+          <t>600:新R055、600:新R085</t>
         </is>
       </c>
     </row>
@@ -31085,12 +31085,12 @@
       </c>
       <c r="B689" s="2" t="inlineStr">
         <is>
-          <t>MG-P31074601A840</t>
+          <t>MG-P2A0C4D9E7326</t>
         </is>
       </c>
       <c r="C689" s="2" t="inlineStr">
         <is>
-          <t>弹卡室</t>
+          <t>座环</t>
         </is>
       </c>
       <c r="D689" s="2" t="inlineStr">
@@ -31112,7 +31112,7 @@
       </c>
       <c r="I689" s="2" t="inlineStr">
         <is>
-          <t>600:新R055、600:新R085</t>
+          <t>600:新R056、600:新R086</t>
         </is>
       </c>
     </row>
@@ -31122,24 +31122,24 @@
       </c>
       <c r="B690" s="2" t="inlineStr">
         <is>
-          <t>MG-P2A0C4D9E7326</t>
+          <t>MG-PAEA256383812</t>
         </is>
       </c>
       <c r="C690" s="2" t="inlineStr">
         <is>
-          <t>座环</t>
+          <t>外管</t>
         </is>
       </c>
       <c r="D690" s="2" t="inlineStr">
         <is>
-          <t>HTW</t>
+          <t>HTW-3m</t>
         </is>
       </c>
       <c r="E690" s="2" t="inlineStr"/>
       <c r="F690" s="2" t="inlineStr"/>
       <c r="G690" s="2" t="inlineStr">
         <is>
-          <t>只</t>
+          <t>根</t>
         </is>
       </c>
       <c r="H690" s="2" t="inlineStr">
@@ -31149,7 +31149,7 @@
       </c>
       <c r="I690" s="2" t="inlineStr">
         <is>
-          <t>600:新R056、600:新R086</t>
+          <t>600:新R057、600:新R058、600:新R087</t>
         </is>
       </c>
     </row>
@@ -31159,24 +31159,24 @@
       </c>
       <c r="B691" s="2" t="inlineStr">
         <is>
-          <t>MG-PAEA256383812</t>
+          <t>MG-PD094CA62AB9B</t>
         </is>
       </c>
       <c r="C691" s="2" t="inlineStr">
         <is>
-          <t>外管</t>
+          <t>内管扶正环</t>
         </is>
       </c>
       <c r="D691" s="2" t="inlineStr">
         <is>
-          <t>HTW-3m</t>
+          <t>HTW</t>
         </is>
       </c>
       <c r="E691" s="2" t="inlineStr"/>
       <c r="F691" s="2" t="inlineStr"/>
       <c r="G691" s="2" t="inlineStr">
         <is>
-          <t>根</t>
+          <t>只</t>
         </is>
       </c>
       <c r="H691" s="2" t="inlineStr">
@@ -31186,7 +31186,7 @@
       </c>
       <c r="I691" s="2" t="inlineStr">
         <is>
-          <t>600:新R057、600:新R058、600:新R087</t>
+          <t>600:新R059、600:新R088</t>
         </is>
       </c>
     </row>
@@ -31196,12 +31196,12 @@
       </c>
       <c r="B692" s="2" t="inlineStr">
         <is>
-          <t>MG-PD094CA62AB9B</t>
+          <t>MG-PEA83AE28485E</t>
         </is>
       </c>
       <c r="C692" s="2" t="inlineStr">
         <is>
-          <t>内管扶正环</t>
+          <t>打捞器（含托卡管）</t>
         </is>
       </c>
       <c r="D692" s="2" t="inlineStr">
@@ -31213,7 +31213,7 @@
       <c r="F692" s="2" t="inlineStr"/>
       <c r="G692" s="2" t="inlineStr">
         <is>
-          <t>只</t>
+          <t>套</t>
         </is>
       </c>
       <c r="H692" s="2" t="inlineStr">
@@ -31223,7 +31223,7 @@
       </c>
       <c r="I692" s="2" t="inlineStr">
         <is>
-          <t>600:新R059、600:新R088</t>
+          <t>600:新R060、600:新R091</t>
         </is>
       </c>
     </row>
@@ -31233,12 +31233,12 @@
       </c>
       <c r="B693" s="2" t="inlineStr">
         <is>
-          <t>MG-PEA83AE28485E</t>
+          <t>MG-P7C847858E3E0</t>
         </is>
       </c>
       <c r="C693" s="2" t="inlineStr">
         <is>
-          <t>打捞器（含托卡管）</t>
+          <t>公锥</t>
         </is>
       </c>
       <c r="D693" s="2" t="inlineStr">
@@ -31250,7 +31250,7 @@
       <c r="F693" s="2" t="inlineStr"/>
       <c r="G693" s="2" t="inlineStr">
         <is>
-          <t>套</t>
+          <t>只</t>
         </is>
       </c>
       <c r="H693" s="2" t="inlineStr">
@@ -31260,7 +31260,7 @@
       </c>
       <c r="I693" s="2" t="inlineStr">
         <is>
-          <t>600:新R060、600:新R091</t>
+          <t>600:新R061、600:新R094</t>
         </is>
       </c>
     </row>
@@ -31270,17 +31270,17 @@
       </c>
       <c r="B694" s="2" t="inlineStr">
         <is>
-          <t>MG-P7C847858E3E0</t>
+          <t>MG-P6FAD17A9779B</t>
         </is>
       </c>
       <c r="C694" s="2" t="inlineStr">
         <is>
-          <t>公锥</t>
+          <t>捞矛头</t>
         </is>
       </c>
       <c r="D694" s="2" t="inlineStr">
         <is>
-          <t>HTW</t>
+          <t>N/H</t>
         </is>
       </c>
       <c r="E694" s="2" t="inlineStr"/>
@@ -31297,7 +31297,7 @@
       </c>
       <c r="I694" s="2" t="inlineStr">
         <is>
-          <t>600:新R061、600:新R094</t>
+          <t>600:新R063、600:新R100</t>
         </is>
       </c>
     </row>
@@ -31307,17 +31307,17 @@
       </c>
       <c r="B695" s="2" t="inlineStr">
         <is>
-          <t>MG-P6FAD17A9779B</t>
+          <t>MG-P48D5B7ABC380</t>
         </is>
       </c>
       <c r="C695" s="2" t="inlineStr">
         <is>
-          <t>捞矛头</t>
+          <t>捞矛头弹簧</t>
         </is>
       </c>
       <c r="D695" s="2" t="inlineStr">
         <is>
-          <t>N/H</t>
+          <t>HTW</t>
         </is>
       </c>
       <c r="E695" s="2" t="inlineStr"/>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="I695" s="2" t="inlineStr">
         <is>
-          <t>600:新R063、600:新R100</t>
+          <t>600:新R064、600:新R102</t>
         </is>
       </c>
     </row>
@@ -31344,12 +31344,12 @@
       </c>
       <c r="B696" s="2" t="inlineStr">
         <is>
-          <t>MG-P48D5B7ABC380</t>
+          <t>MG-P085C15473E19</t>
         </is>
       </c>
       <c r="C696" s="2" t="inlineStr">
         <is>
-          <t>捞矛头弹簧</t>
+          <t>报警胶圈</t>
         </is>
       </c>
       <c r="D696" s="2" t="inlineStr">
@@ -31371,7 +31371,7 @@
       </c>
       <c r="I696" s="2" t="inlineStr">
         <is>
-          <t>600:新R064、600:新R102</t>
+          <t>600:新R065、600:新R104</t>
         </is>
       </c>
     </row>
@@ -31381,12 +31381,12 @@
       </c>
       <c r="B697" s="2" t="inlineStr">
         <is>
-          <t>MG-P085C15473E19</t>
+          <t>MG-PAD753B9D89D3</t>
         </is>
       </c>
       <c r="C697" s="2" t="inlineStr">
         <is>
-          <t>报警胶圈</t>
+          <t>钻具圆柱销</t>
         </is>
       </c>
       <c r="D697" s="2" t="inlineStr">
@@ -31398,7 +31398,7 @@
       <c r="F697" s="2" t="inlineStr"/>
       <c r="G697" s="2" t="inlineStr">
         <is>
-          <t>只</t>
+          <t>套</t>
         </is>
       </c>
       <c r="H697" s="2" t="inlineStr">
@@ -31408,7 +31408,7 @@
       </c>
       <c r="I697" s="2" t="inlineStr">
         <is>
-          <t>600:新R065、600:新R104</t>
+          <t>600:新R066、600:新R109</t>
         </is>
       </c>
     </row>
@@ -31418,12 +31418,12 @@
       </c>
       <c r="B698" s="2" t="inlineStr">
         <is>
-          <t>MG-PAD753B9D89D3</t>
+          <t>MG-PF116DA43F375</t>
         </is>
       </c>
       <c r="C698" s="2" t="inlineStr">
         <is>
-          <t>钻具圆柱销</t>
+          <t>止推轴承</t>
         </is>
       </c>
       <c r="D698" s="2" t="inlineStr">
@@ -31435,7 +31435,7 @@
       <c r="F698" s="2" t="inlineStr"/>
       <c r="G698" s="2" t="inlineStr">
         <is>
-          <t>套</t>
+          <t>盘</t>
         </is>
       </c>
       <c r="H698" s="2" t="inlineStr">
@@ -31445,7 +31445,7 @@
       </c>
       <c r="I698" s="2" t="inlineStr">
         <is>
-          <t>600:新R066、600:新R109</t>
+          <t>600:新R067、600:新R105</t>
         </is>
       </c>
     </row>
@@ -31455,12 +31455,12 @@
       </c>
       <c r="B699" s="2" t="inlineStr">
         <is>
-          <t>MG-PF116DA43F375</t>
+          <t>MG-P993340AF2324</t>
         </is>
       </c>
       <c r="C699" s="2" t="inlineStr">
         <is>
-          <t>止推轴承</t>
+          <t>悬挂轴承</t>
         </is>
       </c>
       <c r="D699" s="2" t="inlineStr">
@@ -31482,7 +31482,7 @@
       </c>
       <c r="I699" s="2" t="inlineStr">
         <is>
-          <t>600:新R067、600:新R105</t>
+          <t>600:新R068、600:新R106</t>
         </is>
       </c>
     </row>
@@ -31492,12 +31492,12 @@
       </c>
       <c r="B700" s="2" t="inlineStr">
         <is>
-          <t>MG-P993340AF2324</t>
+          <t>MG-P6918863F871B</t>
         </is>
       </c>
       <c r="C700" s="2" t="inlineStr">
         <is>
-          <t>悬挂轴承</t>
+          <t>打捞钩</t>
         </is>
       </c>
       <c r="D700" s="2" t="inlineStr">
@@ -31509,7 +31509,7 @@
       <c r="F700" s="2" t="inlineStr"/>
       <c r="G700" s="2" t="inlineStr">
         <is>
-          <t>盘</t>
+          <t>付</t>
         </is>
       </c>
       <c r="H700" s="2" t="inlineStr">
@@ -31519,7 +31519,7 @@
       </c>
       <c r="I700" s="2" t="inlineStr">
         <is>
-          <t>600:新R068、600:新R106</t>
+          <t>600:新R069、600:新R111</t>
         </is>
       </c>
     </row>
@@ -31529,12 +31529,12 @@
       </c>
       <c r="B701" s="2" t="inlineStr">
         <is>
-          <t>MG-P6918863F871B</t>
+          <t>MG-PFB74B4E0AF07</t>
         </is>
       </c>
       <c r="C701" s="2" t="inlineStr">
         <is>
-          <t>打捞钩</t>
+          <t>打捞钩弹簧</t>
         </is>
       </c>
       <c r="D701" s="2" t="inlineStr">
@@ -31546,7 +31546,7 @@
       <c r="F701" s="2" t="inlineStr"/>
       <c r="G701" s="2" t="inlineStr">
         <is>
-          <t>付</t>
+          <t>只</t>
         </is>
       </c>
       <c r="H701" s="2" t="inlineStr">
@@ -31556,7 +31556,7 @@
       </c>
       <c r="I701" s="2" t="inlineStr">
         <is>
-          <t>600:新R069、600:新R111</t>
+          <t>600:新R070、600:新R112</t>
         </is>
       </c>
     </row>
@@ -31566,12 +31566,12 @@
       </c>
       <c r="B702" s="2" t="inlineStr">
         <is>
-          <t>MG-PFB74B4E0AF07</t>
+          <t>MG-P97DDB9B1B9EF</t>
         </is>
       </c>
       <c r="C702" s="2" t="inlineStr">
         <is>
-          <t>打捞钩弹簧</t>
+          <t>内管帽总成</t>
         </is>
       </c>
       <c r="D702" s="2" t="inlineStr">
@@ -31583,7 +31583,7 @@
       <c r="F702" s="2" t="inlineStr"/>
       <c r="G702" s="2" t="inlineStr">
         <is>
-          <t>只</t>
+          <t>套</t>
         </is>
       </c>
       <c r="H702" s="2" t="inlineStr">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="I702" s="2" t="inlineStr">
         <is>
-          <t>600:新R070、600:新R112</t>
+          <t>600:新R071、600:新R110</t>
         </is>
       </c>
     </row>
@@ -31603,12 +31603,12 @@
       </c>
       <c r="B703" s="2" t="inlineStr">
         <is>
-          <t>MG-P97DDB9B1B9EF</t>
+          <t>MG-P9D684BFE0D41</t>
         </is>
       </c>
       <c r="C703" s="2" t="inlineStr">
         <is>
-          <t>内管帽总成</t>
+          <t>弹卡钳</t>
         </is>
       </c>
       <c r="D703" s="2" t="inlineStr">
@@ -31620,7 +31620,7 @@
       <c r="F703" s="2" t="inlineStr"/>
       <c r="G703" s="2" t="inlineStr">
         <is>
-          <t>套</t>
+          <t>付</t>
         </is>
       </c>
       <c r="H703" s="2" t="inlineStr">
@@ -31630,7 +31630,7 @@
       </c>
       <c r="I703" s="2" t="inlineStr">
         <is>
-          <t>600:新R071、600:新R110</t>
+          <t>600:新R072、600:新R107</t>
         </is>
       </c>
     </row>
@@ -31640,12 +31640,12 @@
       </c>
       <c r="B704" s="2" t="inlineStr">
         <is>
-          <t>MG-P9D684BFE0D41</t>
+          <t>MG-P92EBB86B0A88</t>
         </is>
       </c>
       <c r="C704" s="2" t="inlineStr">
         <is>
-          <t>弹卡钳</t>
+          <t>连接块</t>
         </is>
       </c>
       <c r="D704" s="2" t="inlineStr">
@@ -31667,7 +31667,7 @@
       </c>
       <c r="I704" s="2" t="inlineStr">
         <is>
-          <t>600:新R072、600:新R107</t>
+          <t>600:新R073</t>
         </is>
       </c>
     </row>
@@ -31677,12 +31677,12 @@
       </c>
       <c r="B705" s="2" t="inlineStr">
         <is>
-          <t>MG-P92EBB86B0A88</t>
+          <t>MG-P5217D19F0F9A</t>
         </is>
       </c>
       <c r="C705" s="2" t="inlineStr">
         <is>
-          <t>连接块</t>
+          <t>弹卡弹簧</t>
         </is>
       </c>
       <c r="D705" s="2" t="inlineStr">
@@ -31694,7 +31694,7 @@
       <c r="F705" s="2" t="inlineStr"/>
       <c r="G705" s="2" t="inlineStr">
         <is>
-          <t>付</t>
+          <t>只</t>
         </is>
       </c>
       <c r="H705" s="2" t="inlineStr">
@@ -31704,7 +31704,7 @@
       </c>
       <c r="I705" s="2" t="inlineStr">
         <is>
-          <t>600:新R073</t>
+          <t>600:新R074</t>
         </is>
       </c>
     </row>
@@ -31714,12 +31714,12 @@
       </c>
       <c r="B706" s="2" t="inlineStr">
         <is>
-          <t>MG-P5217D19F0F9A</t>
+          <t>MG-P76929538846C</t>
         </is>
       </c>
       <c r="C706" s="2" t="inlineStr">
         <is>
-          <t>弹卡弹簧</t>
+          <t>悬挂环</t>
         </is>
       </c>
       <c r="D706" s="2" t="inlineStr">
@@ -31741,7 +31741,7 @@
       </c>
       <c r="I706" s="2" t="inlineStr">
         <is>
-          <t>600:新R074</t>
+          <t>600:新R075、600:新R103</t>
         </is>
       </c>
     </row>
@@ -31751,12 +31751,12 @@
       </c>
       <c r="B707" s="2" t="inlineStr">
         <is>
-          <t>MG-P76929538846C</t>
+          <t>MG-PC68DD2F4CDD0</t>
         </is>
       </c>
       <c r="C707" s="2" t="inlineStr">
         <is>
-          <t>悬挂环</t>
+          <t>钢球架</t>
         </is>
       </c>
       <c r="D707" s="2" t="inlineStr">
@@ -31778,7 +31778,7 @@
       </c>
       <c r="I707" s="2" t="inlineStr">
         <is>
-          <t>600:新R075、600:新R103</t>
+          <t>600:新R077、600:新R114</t>
         </is>
       </c>
     </row>
@@ -31788,24 +31788,24 @@
       </c>
       <c r="B708" s="2" t="inlineStr">
         <is>
-          <t>MG-PC68DD2F4CDD0</t>
+          <t>MG-PE4CA67954230</t>
         </is>
       </c>
       <c r="C708" s="2" t="inlineStr">
         <is>
-          <t>钢球架</t>
+          <t>内管总成</t>
         </is>
       </c>
       <c r="D708" s="2" t="inlineStr">
         <is>
-          <t>HTW</t>
+          <t>NTW</t>
         </is>
       </c>
       <c r="E708" s="2" t="inlineStr"/>
       <c r="F708" s="2" t="inlineStr"/>
       <c r="G708" s="2" t="inlineStr">
         <is>
-          <t>只</t>
+          <t>套</t>
         </is>
       </c>
       <c r="H708" s="2" t="inlineStr">
@@ -31815,7 +31815,7 @@
       </c>
       <c r="I708" s="2" t="inlineStr">
         <is>
-          <t>600:新R077、600:新R114</t>
+          <t>600:新R080</t>
         </is>
       </c>
     </row>
@@ -31825,12 +31825,12 @@
       </c>
       <c r="B709" s="2" t="inlineStr">
         <is>
-          <t>MG-PE4CA67954230</t>
+          <t>MG-P1536046A35D8</t>
         </is>
       </c>
       <c r="C709" s="2" t="inlineStr">
         <is>
-          <t>内管总成</t>
+          <t>扩孔器</t>
         </is>
       </c>
       <c r="D709" s="2" t="inlineStr">
@@ -31842,7 +31842,7 @@
       <c r="F709" s="2" t="inlineStr"/>
       <c r="G709" s="2" t="inlineStr">
         <is>
-          <t>套</t>
+          <t>只</t>
         </is>
       </c>
       <c r="H709" s="2" t="inlineStr">
@@ -31852,7 +31852,7 @@
       </c>
       <c r="I709" s="2" t="inlineStr">
         <is>
-          <t>600:新R080</t>
+          <t>600:新R089、600:补R064</t>
         </is>
       </c>
     </row>
@@ -31862,24 +31862,24 @@
       </c>
       <c r="B710" s="2" t="inlineStr">
         <is>
-          <t>MG-P1536046A35D8</t>
+          <t>MG-PEB798BF8B36E</t>
         </is>
       </c>
       <c r="C710" s="2" t="inlineStr">
         <is>
-          <t>扩孔器</t>
+          <t>内管自由钳</t>
         </is>
       </c>
       <c r="D710" s="2" t="inlineStr">
         <is>
-          <t>NTW</t>
+          <t>NTW（61）</t>
         </is>
       </c>
       <c r="E710" s="2" t="inlineStr"/>
       <c r="F710" s="2" t="inlineStr"/>
       <c r="G710" s="2" t="inlineStr">
         <is>
-          <t>只</t>
+          <t>把</t>
         </is>
       </c>
       <c r="H710" s="2" t="inlineStr">
@@ -31889,7 +31889,7 @@
       </c>
       <c r="I710" s="2" t="inlineStr">
         <is>
-          <t>600:新R089、600:补R064</t>
+          <t>600:新R092、600:补R100</t>
         </is>
       </c>
     </row>
@@ -31899,17 +31899,17 @@
       </c>
       <c r="B711" s="2" t="inlineStr">
         <is>
-          <t>MG-PEB798BF8B36E</t>
+          <t>MG-P438CE39CF80C</t>
         </is>
       </c>
       <c r="C711" s="2" t="inlineStr">
         <is>
-          <t>内管自由钳</t>
+          <t>外管自由钳</t>
         </is>
       </c>
       <c r="D711" s="2" t="inlineStr">
         <is>
-          <t>NTW（61）</t>
+          <t>NTW（73）</t>
         </is>
       </c>
       <c r="E711" s="2" t="inlineStr"/>
@@ -31926,7 +31926,7 @@
       </c>
       <c r="I711" s="2" t="inlineStr">
         <is>
-          <t>600:新R092、600:补R100</t>
+          <t>600:新R093</t>
         </is>
       </c>
     </row>
@@ -31936,24 +31936,24 @@
       </c>
       <c r="B712" s="2" t="inlineStr">
         <is>
-          <t>MG-P438CE39CF80C</t>
+          <t>MG-PB4C2FFB6D1D0</t>
         </is>
       </c>
       <c r="C712" s="2" t="inlineStr">
         <is>
-          <t>外管自由钳</t>
+          <t>钻具提头</t>
         </is>
       </c>
       <c r="D712" s="2" t="inlineStr">
         <is>
-          <t>NTW（73）</t>
+          <t>NTW</t>
         </is>
       </c>
       <c r="E712" s="2" t="inlineStr"/>
       <c r="F712" s="2" t="inlineStr"/>
       <c r="G712" s="2" t="inlineStr">
         <is>
-          <t>把</t>
+          <t>只</t>
         </is>
       </c>
       <c r="H712" s="2" t="inlineStr">
@@ -31963,7 +31963,7 @@
       </c>
       <c r="I712" s="2" t="inlineStr">
         <is>
-          <t>600:新R093</t>
+          <t>600:新R095</t>
         </is>
       </c>
     </row>
@@ -31973,17 +31973,17 @@
       </c>
       <c r="B713" s="2" t="inlineStr">
         <is>
-          <t>MG-PB4C2FFB6D1D0</t>
+          <t>MG-P1288C6A22782</t>
         </is>
       </c>
       <c r="C713" s="2" t="inlineStr">
         <is>
-          <t>钻具提头</t>
+          <t>变径</t>
         </is>
       </c>
       <c r="D713" s="2" t="inlineStr">
         <is>
-          <t>NTW</t>
+          <t>规格:NTW / HTW;NTW</t>
         </is>
       </c>
       <c r="E713" s="2" t="inlineStr"/>
@@ -32000,7 +32000,7 @@
       </c>
       <c r="I713" s="2" t="inlineStr">
         <is>
-          <t>600:新R095</t>
+          <t>600:新R096、600:新R097</t>
         </is>
       </c>
     </row>
@@ -32010,24 +32010,24 @@
       </c>
       <c r="B714" s="2" t="inlineStr">
         <is>
-          <t>MG-P1288C6A22782</t>
+          <t>MG-PBD54E4BA80AF</t>
         </is>
       </c>
       <c r="C714" s="2" t="inlineStr">
         <is>
-          <t>变径</t>
+          <t>加重器</t>
         </is>
       </c>
       <c r="D714" s="2" t="inlineStr">
         <is>
-          <t>规格:NTW / HTW;NTW</t>
+          <t>NTW</t>
         </is>
       </c>
       <c r="E714" s="2" t="inlineStr"/>
       <c r="F714" s="2" t="inlineStr"/>
       <c r="G714" s="2" t="inlineStr">
         <is>
-          <t>只</t>
+          <t>根</t>
         </is>
       </c>
       <c r="H714" s="2" t="inlineStr">
@@ -32037,7 +32037,7 @@
       </c>
       <c r="I714" s="2" t="inlineStr">
         <is>
-          <t>600:新R096、600:新R097</t>
+          <t>600:新R098</t>
         </is>
       </c>
     </row>
@@ -32047,12 +32047,12 @@
       </c>
       <c r="B715" s="2" t="inlineStr">
         <is>
-          <t>MG-PBD54E4BA80AF</t>
+          <t>MG-P312D2F94FDC2</t>
         </is>
       </c>
       <c r="C715" s="2" t="inlineStr">
         <is>
-          <t>加重器</t>
+          <t>衬圈（定位压块）</t>
         </is>
       </c>
       <c r="D715" s="2" t="inlineStr">
@@ -32064,7 +32064,7 @@
       <c r="F715" s="2" t="inlineStr"/>
       <c r="G715" s="2" t="inlineStr">
         <is>
-          <t>根</t>
+          <t>只</t>
         </is>
       </c>
       <c r="H715" s="2" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="I715" s="2" t="inlineStr">
         <is>
-          <t>600:新R098</t>
+          <t>600:新R101</t>
         </is>
       </c>
     </row>
@@ -32084,12 +32084,12 @@
       </c>
       <c r="B716" s="2" t="inlineStr">
         <is>
-          <t>MG-P312D2F94FDC2</t>
+          <t>MG-PBE7E522A045A</t>
         </is>
       </c>
       <c r="C716" s="2" t="inlineStr">
         <is>
-          <t>衬圈（定位压块）</t>
+          <t>连接板 （涨簧）</t>
         </is>
       </c>
       <c r="D716" s="2" t="inlineStr">
@@ -32101,7 +32101,7 @@
       <c r="F716" s="2" t="inlineStr"/>
       <c r="G716" s="2" t="inlineStr">
         <is>
-          <t>只</t>
+          <t>付</t>
         </is>
       </c>
       <c r="H716" s="2" t="inlineStr">
@@ -32111,7 +32111,7 @@
       </c>
       <c r="I716" s="2" t="inlineStr">
         <is>
-          <t>600:新R101</t>
+          <t>600:新R108</t>
         </is>
       </c>
     </row>
@@ -32121,12 +32121,12 @@
       </c>
       <c r="B717" s="2" t="inlineStr">
         <is>
-          <t>MG-PBE7E522A045A</t>
+          <t>MG-P760F70E8F68C</t>
         </is>
       </c>
       <c r="C717" s="2" t="inlineStr">
         <is>
-          <t>连接板 （涨簧）</t>
+          <t>打捞器销子</t>
         </is>
       </c>
       <c r="D717" s="2" t="inlineStr">
@@ -32138,7 +32138,7 @@
       <c r="F717" s="2" t="inlineStr"/>
       <c r="G717" s="2" t="inlineStr">
         <is>
-          <t>付</t>
+          <t>套</t>
         </is>
       </c>
       <c r="H717" s="2" t="inlineStr">
@@ -32148,7 +32148,7 @@
       </c>
       <c r="I717" s="2" t="inlineStr">
         <is>
-          <t>600:新R108</t>
+          <t>600:新R113</t>
         </is>
       </c>
     </row>
@@ -32158,24 +32158,24 @@
       </c>
       <c r="B718" s="2" t="inlineStr">
         <is>
-          <t>MG-P760F70E8F68C</t>
+          <t>MG-P4FD68E3D3628</t>
         </is>
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>打捞器销子</t>
+          <t>回油滤芯</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
         <is>
-          <t>NTW</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E718" s="2" t="inlineStr"/>
       <c r="F718" s="2" t="inlineStr"/>
       <c r="G718" s="2" t="inlineStr">
         <is>
-          <t>套</t>
+          <t>个</t>
         </is>
       </c>
       <c r="H718" s="2" t="inlineStr">
@@ -32185,7 +32185,7 @@
       </c>
       <c r="I718" s="2" t="inlineStr">
         <is>
-          <t>600:新R113</t>
+          <t>600:新R119、600:新R120</t>
         </is>
       </c>
     </row>
@@ -32195,17 +32195,17 @@
       </c>
       <c r="B719" s="2" t="inlineStr">
         <is>
-          <t>MG-P4FD68E3D3628</t>
+          <t>MG-P064A6E157196</t>
         </is>
       </c>
       <c r="C719" s="2" t="inlineStr">
         <is>
-          <t>回油滤芯</t>
+          <t>吸油滤芯</t>
         </is>
       </c>
       <c r="D719" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>3寸加长</t>
         </is>
       </c>
       <c r="E719" s="2" t="inlineStr"/>
@@ -32222,7 +32222,7 @@
       </c>
       <c r="I719" s="2" t="inlineStr">
         <is>
-          <t>600:新R119、600:新R120</t>
+          <t>600:新R121、600:新R122</t>
         </is>
       </c>
     </row>
@@ -32232,24 +32232,24 @@
       </c>
       <c r="B720" s="2" t="inlineStr">
         <is>
-          <t>MG-P064A6E157196</t>
+          <t>MG-P70983A815D64</t>
         </is>
       </c>
       <c r="C720" s="2" t="inlineStr">
         <is>
-          <t>吸油滤芯</t>
+          <t>潍柴129 KW</t>
         </is>
       </c>
       <c r="D720" s="2" t="inlineStr">
         <is>
-          <t>3寸加长</t>
+          <t>滤芯一套</t>
         </is>
       </c>
       <c r="E720" s="2" t="inlineStr"/>
       <c r="F720" s="2" t="inlineStr"/>
       <c r="G720" s="2" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>套</t>
         </is>
       </c>
       <c r="H720" s="2" t="inlineStr">
@@ -32259,7 +32259,7 @@
       </c>
       <c r="I720" s="2" t="inlineStr">
         <is>
-          <t>600:新R121、600:新R122</t>
+          <t>600:新R123</t>
         </is>
       </c>
     </row>
@@ -32269,24 +32269,24 @@
       </c>
       <c r="B721" s="2" t="inlineStr">
         <is>
-          <t>MG-P70983A815D64</t>
+          <t>MG-P9DF1EA70A0CF</t>
         </is>
       </c>
       <c r="C721" s="2" t="inlineStr">
         <is>
-          <t>潍柴129 KW</t>
+          <t>骨架油封</t>
         </is>
       </c>
       <c r="D721" s="2" t="inlineStr">
         <is>
-          <t>滤芯一套</t>
+          <t>98/120/12</t>
         </is>
       </c>
       <c r="E721" s="2" t="inlineStr"/>
       <c r="F721" s="2" t="inlineStr"/>
       <c r="G721" s="2" t="inlineStr">
         <is>
-          <t>套</t>
+          <t>个</t>
         </is>
       </c>
       <c r="H721" s="2" t="inlineStr">
@@ -32296,7 +32296,7 @@
       </c>
       <c r="I721" s="2" t="inlineStr">
         <is>
-          <t>600:新R123</t>
+          <t>600:新R124、600:新R125、600:新R126</t>
         </is>
       </c>
     </row>
@@ -32306,24 +32306,24 @@
       </c>
       <c r="B722" s="2" t="inlineStr">
         <is>
-          <t>MG-P9DF1EA70A0CF</t>
+          <t>MG-P19F9D7415EE0</t>
         </is>
       </c>
       <c r="C722" s="2" t="inlineStr">
         <is>
-          <t>骨架油封</t>
+          <t>扶正盘</t>
         </is>
       </c>
       <c r="D722" s="2" t="inlineStr">
         <is>
-          <t>98/120/12</t>
+          <t>NTW</t>
         </is>
       </c>
       <c r="E722" s="2" t="inlineStr"/>
       <c r="F722" s="2" t="inlineStr"/>
       <c r="G722" s="2" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>套</t>
         </is>
       </c>
       <c r="H722" s="2" t="inlineStr">
@@ -32333,7 +32333,7 @@
       </c>
       <c r="I722" s="2" t="inlineStr">
         <is>
-          <t>600:新R124、600:新R125、600:新R126</t>
+          <t>600:新R127、600:新R128、600:新R129</t>
         </is>
       </c>
     </row>
@@ -32343,12 +32343,12 @@
       </c>
       <c r="B723" s="2" t="inlineStr">
         <is>
-          <t>MG-P19F9D7415EE0</t>
+          <t>MG-P6F51C5EDADDF</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
         <is>
-          <t>扶正盘</t>
+          <t>卡瓦</t>
         </is>
       </c>
       <c r="D723" s="2" t="inlineStr">
@@ -32370,7 +32370,7 @@
       </c>
       <c r="I723" s="2" t="inlineStr">
         <is>
-          <t>600:新R127、600:新R128、600:新R129</t>
+          <t>600:新R130、600:新R131、600:新R132</t>
         </is>
       </c>
     </row>
@@ -32380,17 +32380,17 @@
       </c>
       <c r="B724" s="2" t="inlineStr">
         <is>
-          <t>MG-P6F51C5EDADDF</t>
+          <t>MG-P75180ED45B08</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>卡瓦</t>
+          <t>尼龙板</t>
         </is>
       </c>
       <c r="D724" s="2" t="inlineStr">
         <is>
-          <t>NTW</t>
+          <t>未列</t>
         </is>
       </c>
       <c r="E724" s="2" t="inlineStr"/>
@@ -32407,7 +32407,7 @@
       </c>
       <c r="I724" s="2" t="inlineStr">
         <is>
-          <t>600:新R130、600:新R131、600:新R132</t>
+          <t>600:新R133</t>
         </is>
       </c>
     </row>
@@ -32417,12 +32417,12 @@
       </c>
       <c r="B725" s="2" t="inlineStr">
         <is>
-          <t>MG-P75180ED45B08</t>
+          <t>MG-PCA08A7388A4D</t>
         </is>
       </c>
       <c r="C725" s="2" t="inlineStr">
         <is>
-          <t>尼龙板</t>
+          <t>油锁</t>
         </is>
       </c>
       <c r="D725" s="2" t="inlineStr">
@@ -32434,7 +32434,7 @@
       <c r="F725" s="2" t="inlineStr"/>
       <c r="G725" s="2" t="inlineStr">
         <is>
-          <t>套</t>
+          <t>个</t>
         </is>
       </c>
       <c r="H725" s="2" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="I725" s="2" t="inlineStr">
         <is>
-          <t>600:新R133</t>
+          <t>600:新R134</t>
         </is>
       </c>
     </row>
@@ -32454,12 +32454,12 @@
       </c>
       <c r="B726" s="2" t="inlineStr">
         <is>
-          <t>MG-PCA08A7388A4D</t>
+          <t>MG-PA93A7C329FEB</t>
         </is>
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>油锁</t>
+          <t>发电表</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
@@ -32481,7 +32481,7 @@
       </c>
       <c r="I726" s="2" t="inlineStr">
         <is>
-          <t>600:新R134</t>
+          <t>600:新R135</t>
         </is>
       </c>
     </row>
@@ -32491,17 +32491,17 @@
       </c>
       <c r="B727" s="2" t="inlineStr">
         <is>
-          <t>MG-PA93A7C329FEB</t>
+          <t>MG-P7D4CC44CFE6B</t>
         </is>
       </c>
       <c r="C727" s="2" t="inlineStr">
         <is>
-          <t>发电表</t>
+          <t>钢丝轮</t>
         </is>
       </c>
       <c r="D727" s="2" t="inlineStr">
         <is>
-          <t>未列</t>
+          <t>钢丝轮（含轴承）</t>
         </is>
       </c>
       <c r="E727" s="2" t="inlineStr"/>
@@ -32518,7 +32518,7 @@
       </c>
       <c r="I727" s="2" t="inlineStr">
         <is>
-          <t>600:新R135</t>
+          <t>600:新R136</t>
         </is>
       </c>
     </row>
@@ -32528,17 +32528,17 @@
       </c>
       <c r="B728" s="2" t="inlineStr">
         <is>
-          <t>MG-P7D4CC44CFE6B</t>
+          <t>MG-PAE518EF59567</t>
         </is>
       </c>
       <c r="C728" s="2" t="inlineStr">
         <is>
-          <t>钢丝轮</t>
+          <t>24V照明灯</t>
         </is>
       </c>
       <c r="D728" s="2" t="inlineStr">
         <is>
-          <t>钢丝轮（含轴承）</t>
+          <t>未列</t>
         </is>
       </c>
       <c r="E728" s="2" t="inlineStr"/>
@@ -32555,7 +32555,7 @@
       </c>
       <c r="I728" s="2" t="inlineStr">
         <is>
-          <t>600:新R136</t>
+          <t>600:新R137</t>
         </is>
       </c>
     </row>
@@ -32565,17 +32565,17 @@
       </c>
       <c r="B729" s="2" t="inlineStr">
         <is>
-          <t>MG-PAE518EF59567</t>
+          <t>MG-PBBC6DEF67A8A</t>
         </is>
       </c>
       <c r="C729" s="2" t="inlineStr">
         <is>
-          <t>24V照明灯</t>
+          <t>保险丝</t>
         </is>
       </c>
       <c r="D729" s="2" t="inlineStr">
         <is>
-          <t>未列</t>
+          <t>7.5/10/15/20/25/30</t>
         </is>
       </c>
       <c r="E729" s="2" t="inlineStr"/>
@@ -32592,7 +32592,7 @@
       </c>
       <c r="I729" s="2" t="inlineStr">
         <is>
-          <t>600:新R137</t>
+          <t>600:新R138</t>
         </is>
       </c>
     </row>
@@ -32602,17 +32602,17 @@
       </c>
       <c r="B730" s="2" t="inlineStr">
         <is>
-          <t>MG-PBBC6DEF67A8A</t>
+          <t>MG-P199843143D9C</t>
         </is>
       </c>
       <c r="C730" s="2" t="inlineStr">
         <is>
-          <t>保险丝</t>
+          <t>回水开关</t>
         </is>
       </c>
       <c r="D730" s="2" t="inlineStr">
         <is>
-          <t>7.5/10/15/20/25/30</t>
+          <t>未列</t>
         </is>
       </c>
       <c r="E730" s="2" t="inlineStr"/>
@@ -32629,7 +32629,7 @@
       </c>
       <c r="I730" s="2" t="inlineStr">
         <is>
-          <t>600:新R138</t>
+          <t>600:新R139</t>
         </is>
       </c>
     </row>
@@ -32639,12 +32639,12 @@
       </c>
       <c r="B731" s="2" t="inlineStr">
         <is>
-          <t>MG-P199843143D9C</t>
+          <t>MG-P905FD71B57C2</t>
         </is>
       </c>
       <c r="C731" s="2" t="inlineStr">
         <is>
-          <t>回水开关</t>
+          <t>联轴器</t>
         </is>
       </c>
       <c r="D731" s="2" t="inlineStr">
@@ -32666,7 +32666,7 @@
       </c>
       <c r="I731" s="2" t="inlineStr">
         <is>
-          <t>600:新R139</t>
+          <t>600:新R140</t>
         </is>
       </c>
     </row>
@@ -32676,12 +32676,12 @@
       </c>
       <c r="B732" s="2" t="inlineStr">
         <is>
-          <t>MG-P905FD71B57C2</t>
+          <t>MG-P80229906BB90</t>
         </is>
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>联轴器</t>
+          <t>轴压阀芯加旋钮</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
@@ -32693,7 +32693,7 @@
       <c r="F732" s="2" t="inlineStr"/>
       <c r="G732" s="2" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>套</t>
         </is>
       </c>
       <c r="H732" s="2" t="inlineStr">
@@ -32703,7 +32703,7 @@
       </c>
       <c r="I732" s="2" t="inlineStr">
         <is>
-          <t>600:新R140</t>
+          <t>600:新R141</t>
         </is>
       </c>
     </row>
@@ -32713,12 +32713,12 @@
       </c>
       <c r="B733" s="2" t="inlineStr">
         <is>
-          <t>MG-P80229906BB90</t>
+          <t>MG-P8586D5A96819</t>
         </is>
       </c>
       <c r="C733" s="2" t="inlineStr">
         <is>
-          <t>轴压阀芯加旋钮</t>
+          <t>齿轮油观察口</t>
         </is>
       </c>
       <c r="D733" s="2" t="inlineStr">
@@ -32730,7 +32730,7 @@
       <c r="F733" s="2" t="inlineStr"/>
       <c r="G733" s="2" t="inlineStr">
         <is>
-          <t>套</t>
+          <t>个</t>
         </is>
       </c>
       <c r="H733" s="2" t="inlineStr">
@@ -32740,7 +32740,7 @@
       </c>
       <c r="I733" s="2" t="inlineStr">
         <is>
-          <t>600:新R141</t>
+          <t>600:新R142</t>
         </is>
       </c>
     </row>
@@ -32750,12 +32750,12 @@
       </c>
       <c r="B734" s="2" t="inlineStr">
         <is>
-          <t>MG-P8586D5A96819</t>
+          <t>MG-P50F85E86C940</t>
         </is>
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>齿轮油观察口</t>
+          <t>报钳阀</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
@@ -32767,7 +32767,7 @@
       <c r="F734" s="2" t="inlineStr"/>
       <c r="G734" s="2" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>组</t>
         </is>
       </c>
       <c r="H734" s="2" t="inlineStr">
@@ -32777,7 +32777,7 @@
       </c>
       <c r="I734" s="2" t="inlineStr">
         <is>
-          <t>600:新R142</t>
+          <t>600:新R143</t>
         </is>
       </c>
     </row>
@@ -32787,12 +32787,12 @@
       </c>
       <c r="B735" s="2" t="inlineStr">
         <is>
-          <t>MG-P50F85E86C940</t>
+          <t>MG-P84ABBFA6E480</t>
         </is>
       </c>
       <c r="C735" s="2" t="inlineStr">
         <is>
-          <t>报钳阀</t>
+          <t>手柄定位组件</t>
         </is>
       </c>
       <c r="D735" s="2" t="inlineStr">
@@ -32814,7 +32814,7 @@
       </c>
       <c r="I735" s="2" t="inlineStr">
         <is>
-          <t>600:新R143</t>
+          <t>600:新R144</t>
         </is>
       </c>
     </row>
@@ -32824,24 +32824,24 @@
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>MG-P84ABBFA6E480</t>
+          <t>MG-P3778F3A0D9AE</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>手柄定位组件</t>
+          <t>泥浆泵缸套</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
         <is>
-          <t>未列</t>
+          <t>原PDF未列规格</t>
         </is>
       </c>
       <c r="E736" s="2" t="inlineStr"/>
       <c r="F736" s="2" t="inlineStr"/>
       <c r="G736" s="2" t="inlineStr">
         <is>
-          <t>组</t>
+          <t>件</t>
         </is>
       </c>
       <c r="H736" s="2" t="inlineStr">
@@ -32851,7 +32851,7 @@
       </c>
       <c r="I736" s="2" t="inlineStr">
         <is>
-          <t>600:新R144</t>
+          <t>600:补R017</t>
         </is>
       </c>
     </row>
@@ -32861,12 +32861,12 @@
       </c>
       <c r="B737" s="2" t="inlineStr">
         <is>
-          <t>MG-P3778F3A0D9AE</t>
+          <t>MG-PDC42F829F77E</t>
         </is>
       </c>
       <c r="C737" s="2" t="inlineStr">
         <is>
-          <t>泥浆泵缸套</t>
+          <t>皮碗</t>
         </is>
       </c>
       <c r="D737" s="2" t="inlineStr">
@@ -32888,7 +32888,7 @@
       </c>
       <c r="I737" s="2" t="inlineStr">
         <is>
-          <t>600:补R017</t>
+          <t>600:补R018</t>
         </is>
       </c>
     </row>
@@ -32898,12 +32898,12 @@
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>MG-PDC42F829F77E</t>
+          <t>MG-P6EC7ECB13150</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>皮碗</t>
+          <t>缸套垫</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
@@ -32925,7 +32925,7 @@
       </c>
       <c r="I738" s="2" t="inlineStr">
         <is>
-          <t>600:补R018</t>
+          <t>600:补R019</t>
         </is>
       </c>
     </row>
@@ -32935,12 +32935,12 @@
       </c>
       <c r="B739" s="2" t="inlineStr">
         <is>
-          <t>MG-P6EC7ECB13150</t>
+          <t>MG-P3E34E2B450B7</t>
         </is>
       </c>
       <c r="C739" s="2" t="inlineStr">
         <is>
-          <t>缸套垫</t>
+          <t>钢球座</t>
         </is>
       </c>
       <c r="D739" s="2" t="inlineStr">
@@ -32962,7 +32962,7 @@
       </c>
       <c r="I739" s="2" t="inlineStr">
         <is>
-          <t>600:补R019</t>
+          <t>600:补R021</t>
         </is>
       </c>
     </row>
@@ -32972,12 +32972,12 @@
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>MG-P3E34E2B450B7</t>
+          <t>MG-P1BD8F702B34A</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>钢球座</t>
+          <t>组合油封</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -32989,7 +32989,7 @@
       <c r="F740" s="2" t="inlineStr"/>
       <c r="G740" s="2" t="inlineStr">
         <is>
-          <t>件</t>
+          <t>套</t>
         </is>
       </c>
       <c r="H740" s="2" t="inlineStr">
@@ -32999,7 +32999,7 @@
       </c>
       <c r="I740" s="2" t="inlineStr">
         <is>
-          <t>600:补R021</t>
+          <t>600:补R022</t>
         </is>
       </c>
     </row>
@@ -33009,12 +33009,12 @@
       </c>
       <c r="B741" s="2" t="inlineStr">
         <is>
-          <t>MG-P1BD8F702B34A</t>
+          <t>MG-P2612A188D148</t>
         </is>
       </c>
       <c r="C741" s="2" t="inlineStr">
         <is>
-          <t>组合油封</t>
+          <t>缸盖O型圈</t>
         </is>
       </c>
       <c r="D741" s="2" t="inlineStr">
@@ -33026,7 +33026,7 @@
       <c r="F741" s="2" t="inlineStr"/>
       <c r="G741" s="2" t="inlineStr">
         <is>
-          <t>套</t>
+          <t>件</t>
         </is>
       </c>
       <c r="H741" s="2" t="inlineStr">
@@ -33036,7 +33036,7 @@
       </c>
       <c r="I741" s="2" t="inlineStr">
         <is>
-          <t>600:补R022</t>
+          <t>600:补R023</t>
         </is>
       </c>
     </row>
@@ -33046,17 +33046,17 @@
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>MG-P2612A188D148</t>
+          <t>MG-P54347A03B82C</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>缸盖O型圈</t>
+          <t>扶正器轴承</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
         <is>
-          <t>原PDF未列规格</t>
+          <t>61821</t>
         </is>
       </c>
       <c r="E742" s="2" t="inlineStr"/>
@@ -33073,7 +33073,7 @@
       </c>
       <c r="I742" s="2" t="inlineStr">
         <is>
-          <t>600:补R023</t>
+          <t>600:补R024</t>
         </is>
       </c>
     </row>
@@ -33083,17 +33083,17 @@
       </c>
       <c r="B743" s="2" t="inlineStr">
         <is>
-          <t>MG-P54347A03B82C</t>
+          <t>MG-PEE9553F2D29C</t>
         </is>
       </c>
       <c r="C743" s="2" t="inlineStr">
         <is>
-          <t>扶正器轴承</t>
+          <t>钻具头总成轴承</t>
         </is>
       </c>
       <c r="D743" s="2" t="inlineStr">
         <is>
-          <t>61821</t>
+          <t>51305</t>
         </is>
       </c>
       <c r="E743" s="2" t="inlineStr"/>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="I743" s="2" t="inlineStr">
         <is>
-          <t>600:补R024</t>
+          <t>600:补R025、600:补R026</t>
         </is>
       </c>
     </row>
@@ -33120,24 +33120,24 @@
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>MG-PEE9553F2D29C</t>
+          <t>MG-PB5BBFD6B12F4</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>钻具头总成轴承</t>
+          <t>植物胶</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
         <is>
-          <t>51305</t>
+          <t>原PDF未列规格</t>
         </is>
       </c>
       <c r="E744" s="2" t="inlineStr"/>
       <c r="F744" s="2" t="inlineStr"/>
       <c r="G744" s="2" t="inlineStr">
         <is>
-          <t>件</t>
+          <t>吨</t>
         </is>
       </c>
       <c r="H744" s="2" t="inlineStr">
@@ -33147,7 +33147,7 @@
       </c>
       <c r="I744" s="2" t="inlineStr">
         <is>
-          <t>600:补R025、600:补R026</t>
+          <t>600:补R028</t>
         </is>
       </c>
     </row>
@@ -33157,12 +33157,12 @@
       </c>
       <c r="B745" s="2" t="inlineStr">
         <is>
-          <t>MG-PB5BBFD6B12F4</t>
+          <t>MG-P61C5DF2B4DD1</t>
         </is>
       </c>
       <c r="C745" s="2" t="inlineStr">
         <is>
-          <t>植物胶</t>
+          <t>堵漏剂25KG/袋</t>
         </is>
       </c>
       <c r="D745" s="2" t="inlineStr">
@@ -33174,7 +33174,7 @@
       <c r="F745" s="2" t="inlineStr"/>
       <c r="G745" s="2" t="inlineStr">
         <is>
-          <t>吨</t>
+          <t>袋</t>
         </is>
       </c>
       <c r="H745" s="2" t="inlineStr">
@@ -33184,7 +33184,7 @@
       </c>
       <c r="I745" s="2" t="inlineStr">
         <is>
-          <t>600:补R028</t>
+          <t>600:补R030</t>
         </is>
       </c>
     </row>
@@ -33194,24 +33194,24 @@
       </c>
       <c r="B746" s="2" t="inlineStr">
         <is>
-          <t>MG-P61C5DF2B4DD1</t>
+          <t>MG-PF6EBB2663451</t>
         </is>
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>堵漏剂25KG/袋</t>
+          <t>丝扣油</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
         <is>
-          <t>原PDF未列规格</t>
+          <t>原PDF未列规格；18千克/桶</t>
         </is>
       </c>
       <c r="E746" s="2" t="inlineStr"/>
       <c r="F746" s="2" t="inlineStr"/>
       <c r="G746" s="2" t="inlineStr">
         <is>
-          <t>袋</t>
+          <t>桶</t>
         </is>
       </c>
       <c r="H746" s="2" t="inlineStr">
@@ -33221,7 +33221,7 @@
       </c>
       <c r="I746" s="2" t="inlineStr">
         <is>
-          <t>600:补R030</t>
+          <t>600:补R032</t>
         </is>
       </c>
     </row>
@@ -33231,12 +33231,12 @@
       </c>
       <c r="B747" s="2" t="inlineStr">
         <is>
-          <t>MG-PF6EBB2663451</t>
+          <t>MG-P816EA459EDB7</t>
         </is>
       </c>
       <c r="C747" s="2" t="inlineStr">
         <is>
-          <t>丝扣油</t>
+          <t>钻杆油</t>
         </is>
       </c>
       <c r="D747" s="2" t="inlineStr">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="I747" s="2" t="inlineStr">
         <is>
-          <t>600:补R032</t>
+          <t>600:补R034</t>
         </is>
       </c>
     </row>
@@ -33268,24 +33268,24 @@
       </c>
       <c r="B748" s="2" t="inlineStr">
         <is>
-          <t>MG-P816EA459EDB7</t>
+          <t>MG-P7868BE3B65A2</t>
         </is>
       </c>
       <c r="C748" s="2" t="inlineStr">
         <is>
-          <t>钻杆油</t>
+          <t>抽水机密封</t>
         </is>
       </c>
       <c r="D748" s="2" t="inlineStr">
         <is>
-          <t>原PDF未列规格；18千克/桶</t>
+          <t>原PDF未列规格</t>
         </is>
       </c>
       <c r="E748" s="2" t="inlineStr"/>
       <c r="F748" s="2" t="inlineStr"/>
       <c r="G748" s="2" t="inlineStr">
         <is>
-          <t>桶</t>
+          <t>件</t>
         </is>
       </c>
       <c r="H748" s="2" t="inlineStr">
@@ -33295,7 +33295,7 @@
       </c>
       <c r="I748" s="2" t="inlineStr">
         <is>
-          <t>600:补R034</t>
+          <t>600:补R035</t>
         </is>
       </c>
     </row>
@@ -33305,12 +33305,12 @@
       </c>
       <c r="B749" s="2" t="inlineStr">
         <is>
-          <t>MG-P7868BE3B65A2</t>
+          <t>MG-P3C23EE1D2EAE</t>
         </is>
       </c>
       <c r="C749" s="2" t="inlineStr">
         <is>
-          <t>抽水机密封</t>
+          <t>PVC水管110mm</t>
         </is>
       </c>
       <c r="D749" s="2" t="inlineStr">
@@ -33322,7 +33322,7 @@
       <c r="F749" s="2" t="inlineStr"/>
       <c r="G749" s="2" t="inlineStr">
         <is>
-          <t>件</t>
+          <t>米</t>
         </is>
       </c>
       <c r="H749" s="2" t="inlineStr">
@@ -33332,7 +33332,7 @@
       </c>
       <c r="I749" s="2" t="inlineStr">
         <is>
-          <t>600:补R035</t>
+          <t>600:补R036</t>
         </is>
       </c>
     </row>
@@ -33342,12 +33342,12 @@
       </c>
       <c r="B750" s="2" t="inlineStr">
         <is>
-          <t>MG-P3C23EE1D2EAE</t>
+          <t>MG-P1EB2906D3FD6</t>
         </is>
       </c>
       <c r="C750" s="2" t="inlineStr">
         <is>
-          <t>PVC水管110mm</t>
+          <t>PVC水管接头（直接）</t>
         </is>
       </c>
       <c r="D750" s="2" t="inlineStr">
@@ -33359,7 +33359,7 @@
       <c r="F750" s="2" t="inlineStr"/>
       <c r="G750" s="2" t="inlineStr">
         <is>
-          <t>米</t>
+          <t>件</t>
         </is>
       </c>
       <c r="H750" s="2" t="inlineStr">
@@ -33369,7 +33369,7 @@
       </c>
       <c r="I750" s="2" t="inlineStr">
         <is>
-          <t>600:补R036</t>
+          <t>600:补R037</t>
         </is>
       </c>
     </row>
@@ -33379,24 +33379,24 @@
       </c>
       <c r="B751" s="2" t="inlineStr">
         <is>
-          <t>MG-P1EB2906D3FD6</t>
+          <t>MG-P25F6A8F59748</t>
         </is>
       </c>
       <c r="C751" s="2" t="inlineStr">
         <is>
-          <t>PVC水管接头（直接）</t>
+          <t>机油</t>
         </is>
       </c>
       <c r="D751" s="2" t="inlineStr">
         <is>
-          <t>原PDF未列规格</t>
+          <t>桶容及牌号未列</t>
         </is>
       </c>
       <c r="E751" s="2" t="inlineStr"/>
       <c r="F751" s="2" t="inlineStr"/>
       <c r="G751" s="2" t="inlineStr">
         <is>
-          <t>件</t>
+          <t>桶</t>
         </is>
       </c>
       <c r="H751" s="2" t="inlineStr">
@@ -33406,7 +33406,7 @@
       </c>
       <c r="I751" s="2" t="inlineStr">
         <is>
-          <t>600:补R037</t>
+          <t>600:补R040</t>
         </is>
       </c>
     </row>
@@ -33416,12 +33416,12 @@
       </c>
       <c r="B752" s="2" t="inlineStr">
         <is>
-          <t>MG-P25F6A8F59748</t>
+          <t>MG-PE31740D78B7B</t>
         </is>
       </c>
       <c r="C752" s="2" t="inlineStr">
         <is>
-          <t>机油</t>
+          <t>液压油</t>
         </is>
       </c>
       <c r="D752" s="2" t="inlineStr">
@@ -33443,7 +33443,7 @@
       </c>
       <c r="I752" s="2" t="inlineStr">
         <is>
-          <t>600:补R040</t>
+          <t>600:补R041</t>
         </is>
       </c>
     </row>
@@ -33453,24 +33453,24 @@
       </c>
       <c r="B753" s="2" t="inlineStr">
         <is>
-          <t>MG-PE31740D78B7B</t>
+          <t>MG-PD3C6740B8D38</t>
         </is>
       </c>
       <c r="C753" s="2" t="inlineStr">
         <is>
-          <t>液压油</t>
+          <t>卡簧挡圈</t>
         </is>
       </c>
       <c r="D753" s="2" t="inlineStr">
         <is>
-          <t>桶容及牌号未列</t>
+          <t>NTW</t>
         </is>
       </c>
       <c r="E753" s="2" t="inlineStr"/>
       <c r="F753" s="2" t="inlineStr"/>
       <c r="G753" s="2" t="inlineStr">
         <is>
-          <t>桶</t>
+          <t>件</t>
         </is>
       </c>
       <c r="H753" s="2" t="inlineStr">
@@ -33480,7 +33480,7 @@
       </c>
       <c r="I753" s="2" t="inlineStr">
         <is>
-          <t>600:补R041</t>
+          <t>600:补R049、600:补R067</t>
         </is>
       </c>
     </row>
@@ -33490,12 +33490,12 @@
       </c>
       <c r="B754" s="2" t="inlineStr">
         <is>
-          <t>MG-PD3C6740B8D38</t>
+          <t>MG-P13505831C99E</t>
         </is>
       </c>
       <c r="C754" s="2" t="inlineStr">
         <is>
-          <t>卡簧挡圈</t>
+          <t>扶正器</t>
         </is>
       </c>
       <c r="D754" s="2" t="inlineStr">
@@ -33517,7 +33517,7 @@
       </c>
       <c r="I754" s="2" t="inlineStr">
         <is>
-          <t>600:补R049、600:补R067</t>
+          <t>600:补R052、600:补R070</t>
         </is>
       </c>
     </row>
@@ -33527,17 +33527,17 @@
       </c>
       <c r="B755" s="2" t="inlineStr">
         <is>
-          <t>MG-P13505831C99E</t>
+          <t>MG-P2692C7091757</t>
         </is>
       </c>
       <c r="C755" s="2" t="inlineStr">
         <is>
-          <t>扶正器</t>
+          <t>金刚石钻头</t>
         </is>
       </c>
       <c r="D755" s="2" t="inlineStr">
         <is>
-          <t>NTW</t>
+          <t>HTW</t>
         </is>
       </c>
       <c r="E755" s="2" t="inlineStr"/>
@@ -33554,7 +33554,7 @@
       </c>
       <c r="I755" s="2" t="inlineStr">
         <is>
-          <t>600:补R052、600:补R070</t>
+          <t>600:补R063</t>
         </is>
       </c>
     </row>
@@ -33564,17 +33564,17 @@
       </c>
       <c r="B756" s="2" t="inlineStr">
         <is>
-          <t>MG-P2692C7091757</t>
+          <t>MG-P8BBFEFECE05E</t>
         </is>
       </c>
       <c r="C756" s="2" t="inlineStr">
         <is>
-          <t>金刚石钻头</t>
+          <t>吸水龙头</t>
         </is>
       </c>
       <c r="D756" s="2" t="inlineStr">
         <is>
-          <t>HTW</t>
+          <t>原PDF未列规格</t>
         </is>
       </c>
       <c r="E756" s="2" t="inlineStr"/>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="I756" s="2" t="inlineStr">
         <is>
-          <t>600:补R063</t>
+          <t>600:补R078</t>
         </is>
       </c>
     </row>
@@ -33601,12 +33601,12 @@
       </c>
       <c r="B757" s="2" t="inlineStr">
         <is>
-          <t>MG-P8BBFEFECE05E</t>
+          <t>MG-PBCA306C640E0</t>
         </is>
       </c>
       <c r="C757" s="2" t="inlineStr">
         <is>
-          <t>吸水龙头</t>
+          <t>柴油机减震垫</t>
         </is>
       </c>
       <c r="D757" s="2" t="inlineStr">
@@ -33628,7 +33628,7 @@
       </c>
       <c r="I757" s="2" t="inlineStr">
         <is>
-          <t>600:补R078</t>
+          <t>600:补R079</t>
         </is>
       </c>
     </row>
@@ -33638,12 +33638,12 @@
       </c>
       <c r="B758" s="2" t="inlineStr">
         <is>
-          <t>MG-PBCA306C640E0</t>
+          <t>MG-P37BF23286259</t>
         </is>
       </c>
       <c r="C758" s="2" t="inlineStr">
         <is>
-          <t>柴油机减震垫</t>
+          <t>曲轴瓦</t>
         </is>
       </c>
       <c r="D758" s="2" t="inlineStr">
@@ -33665,7 +33665,7 @@
       </c>
       <c r="I758" s="2" t="inlineStr">
         <is>
-          <t>600:补R079</t>
+          <t>600:补R081</t>
         </is>
       </c>
     </row>
@@ -33675,12 +33675,12 @@
       </c>
       <c r="B759" s="2" t="inlineStr">
         <is>
-          <t>MG-P37BF23286259</t>
+          <t>MG-P4609EA0E8D50</t>
         </is>
       </c>
       <c r="C759" s="2" t="inlineStr">
         <is>
-          <t>曲轴瓦</t>
+          <t>皮碗座</t>
         </is>
       </c>
       <c r="D759" s="2" t="inlineStr">
@@ -33702,7 +33702,7 @@
       </c>
       <c r="I759" s="2" t="inlineStr">
         <is>
-          <t>600:补R081</t>
+          <t>600:补R084</t>
         </is>
       </c>
     </row>
@@ -33712,24 +33712,24 @@
       </c>
       <c r="B760" s="2" t="inlineStr">
         <is>
-          <t>MG-P4609EA0E8D50</t>
+          <t>MG-P12F7DAC69127</t>
         </is>
       </c>
       <c r="C760" s="2" t="inlineStr">
         <is>
-          <t>皮碗座</t>
+          <t>吊带</t>
         </is>
       </c>
       <c r="D760" s="2" t="inlineStr">
         <is>
-          <t>原PDF未列规格</t>
+          <t>5吨</t>
         </is>
       </c>
       <c r="E760" s="2" t="inlineStr"/>
       <c r="F760" s="2" t="inlineStr"/>
       <c r="G760" s="2" t="inlineStr">
         <is>
-          <t>件</t>
+          <t>条</t>
         </is>
       </c>
       <c r="H760" s="2" t="inlineStr">
@@ -33739,7 +33739,7 @@
       </c>
       <c r="I760" s="2" t="inlineStr">
         <is>
-          <t>600:补R084</t>
+          <t>600:补R086</t>
         </is>
       </c>
     </row>
@@ -33749,24 +33749,24 @@
       </c>
       <c r="B761" s="2" t="inlineStr">
         <is>
-          <t>MG-P12F7DAC69127</t>
+          <t>MG-P1E1EF37865AB</t>
         </is>
       </c>
       <c r="C761" s="2" t="inlineStr">
         <is>
-          <t>吊带</t>
+          <t>锂电角磨机</t>
         </is>
       </c>
       <c r="D761" s="2" t="inlineStr">
         <is>
-          <t>5吨</t>
+          <t>未列</t>
         </is>
       </c>
       <c r="E761" s="2" t="inlineStr"/>
       <c r="F761" s="2" t="inlineStr"/>
       <c r="G761" s="2" t="inlineStr">
         <is>
-          <t>条</t>
+          <t>台</t>
         </is>
       </c>
       <c r="H761" s="2" t="inlineStr">
@@ -33776,7 +33776,7 @@
       </c>
       <c r="I761" s="2" t="inlineStr">
         <is>
-          <t>600:补R086</t>
+          <t>600:补R087</t>
         </is>
       </c>
     </row>
@@ -33786,17 +33786,17 @@
       </c>
       <c r="B762" s="2" t="inlineStr">
         <is>
-          <t>MG-P1E1EF37865AB</t>
+          <t>MG-P3D058B13C32B</t>
         </is>
       </c>
       <c r="C762" s="2" t="inlineStr">
         <is>
-          <t>锂电角磨机</t>
+          <t>便携式小型家用电焊机</t>
         </is>
       </c>
       <c r="D762" s="2" t="inlineStr">
         <is>
-          <t>未列</t>
+          <t>220V</t>
         </is>
       </c>
       <c r="E762" s="2" t="inlineStr"/>
@@ -33813,7 +33813,7 @@
       </c>
       <c r="I762" s="2" t="inlineStr">
         <is>
-          <t>600:补R087</t>
+          <t>600:补R088</t>
         </is>
       </c>
     </row>
@@ -33823,24 +33823,24 @@
       </c>
       <c r="B763" s="2" t="inlineStr">
         <is>
-          <t>MG-P3D058B13C32B</t>
+          <t>MG-P1B2F3E265D09</t>
         </is>
       </c>
       <c r="C763" s="2" t="inlineStr">
         <is>
-          <t>便携式小型家用电焊机</t>
+          <t>提引器</t>
         </is>
       </c>
       <c r="D763" s="2" t="inlineStr">
         <is>
-          <t>220V</t>
+          <t>HTW</t>
         </is>
       </c>
       <c r="E763" s="2" t="inlineStr"/>
       <c r="F763" s="2" t="inlineStr"/>
       <c r="G763" s="2" t="inlineStr">
         <is>
-          <t>台</t>
+          <t>套</t>
         </is>
       </c>
       <c r="H763" s="2" t="inlineStr">
@@ -33850,7 +33850,7 @@
       </c>
       <c r="I763" s="2" t="inlineStr">
         <is>
-          <t>600:补R088</t>
+          <t>600:补R097</t>
         </is>
       </c>
     </row>
@@ -33860,17 +33860,17 @@
       </c>
       <c r="B764" s="2" t="inlineStr">
         <is>
-          <t>MG-P1B2F3E265D09</t>
+          <t>MG-PBB0196BB5F5F</t>
         </is>
       </c>
       <c r="C764" s="2" t="inlineStr">
         <is>
-          <t>提引器</t>
+          <t>打捞器维修包</t>
         </is>
       </c>
       <c r="D764" s="2" t="inlineStr">
         <is>
-          <t>HTW</t>
+          <t>NTW</t>
         </is>
       </c>
       <c r="E764" s="2" t="inlineStr"/>
@@ -33887,49 +33887,12 @@
       </c>
       <c r="I764" s="2" t="inlineStr">
         <is>
-          <t>600:补R097</t>
-        </is>
-      </c>
-    </row>
-    <row r="765">
-      <c r="A765" s="2" t="n">
-        <v>764</v>
-      </c>
-      <c r="B765" s="2" t="inlineStr">
-        <is>
-          <t>MG-PBB0196BB5F5F</t>
-        </is>
-      </c>
-      <c r="C765" s="2" t="inlineStr">
-        <is>
-          <t>打捞器维修包</t>
-        </is>
-      </c>
-      <c r="D765" s="2" t="inlineStr">
-        <is>
-          <t>NTW</t>
-        </is>
-      </c>
-      <c r="E765" s="2" t="inlineStr"/>
-      <c r="F765" s="2" t="inlineStr"/>
-      <c r="G765" s="2" t="inlineStr">
-        <is>
-          <t>套</t>
-        </is>
-      </c>
-      <c r="H765" s="2" t="inlineStr">
-        <is>
-          <t>勘探钻机</t>
-        </is>
-      </c>
-      <c r="I765" s="2" t="inlineStr">
-        <is>
           <t>600:补R104</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I765"/>
+  <autoFilter ref="A1:I764"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33963,7 +33926,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>给「商品清单」里 815 个商品人工挑图:主图必须,详情图有则带。拿法与 2026-07-27 央企专区手动补图那批相同。</t>
+          <t>给「商品清单」里 763 个商品人工挑图:主图必须,详情图有则带。拿法与 2026-07-27 央企专区手动补图那批相同。</t>
         </is>
       </c>
     </row>
